--- a/XBRL-template-MFRS/Company/07-SOCF-Indirect.xlsx
+++ b/XBRL-template-MFRS/Company/07-SOCF-Indirect.xlsx
@@ -968,11 +968,11 @@
         </is>
       </c>
       <c r="B36" s="34">
-        <f>1*B28+1*B29+1*B30+1*B31+1*B32+1*B33+1*B34+1*B35</f>
+        <f>1*B27+1*B28+1*B29+1*B30+1*B31+1*B32+1*B33+1*B34+1*B35</f>
         <v/>
       </c>
       <c r="C36" s="34">
-        <f>1*C28+1*C29+1*C30+1*C31+1*C32+1*C33+1*C34+1*C35</f>
+        <f>1*C27+1*C28+1*C29+1*C30+1*C31+1*C32+1*C33+1*C34+1*C35</f>
         <v/>
       </c>
       <c r="D36" s="40" t="n"/>
@@ -1196,11 +1196,11 @@
         </is>
       </c>
       <c r="B57" s="34">
-        <f>1*B11+1*B12+-1*B13+1*B14+-1*B15+1*B16+-1*B17+1*B18+1*B19+1*B20+-1*B21+1*B22+-1*B23+-1*B24+1*B25+1*B56+-1*B60+-1*B41+-1*B42+-1*B43+-1*B44+-1*B45+1*B46+1*B54+1*B55+1*B56</f>
+        <f>1*B11+1*B12+-1*B13+1*B14+-1*B15+1*B16+-1*B17+1*B18+1*B19+1*B20+-1*B21+1*B22+-1*B23+-1*B24+1*B25+1*B36+-1*B40+-1*B41+-1*B42+-1*B43+-1*B44+-1*B45+1*B46+1*B54+1*B55+1*B56</f>
         <v/>
       </c>
       <c r="C57" s="34">
-        <f>1*C11+1*C12+-1*C13+1*C14+-1*C15+1*C16+-1*C17+1*C18+1*C19+1*C20+-1*C21+1*C22+-1*C23+-1*C24+1*C25+1*C56+-1*C60+-1*C41+-1*C42+-1*C43+-1*C44+-1*C45+1*C46+1*C54+1*C55+1*C56</f>
+        <f>1*C11+1*C12+-1*C13+1*C14+-1*C15+1*C16+-1*C17+1*C18+1*C19+1*C20+-1*C21+1*C22+-1*C23+-1*C24+1*C25+1*C36+-1*C40+-1*C41+-1*C42+-1*C43+-1*C44+-1*C45+1*C46+1*C54+1*C55+1*C56</f>
         <v/>
       </c>
       <c r="D57" s="40" t="n"/>
